--- a/DOC/XCSS_SIZEING/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
+++ b/DOC/XCSS_SIZEING/(분석,방안) NexacroK-상대단위(em,rem) 확장 지원.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tobesoft\Desktop\em,rem\k\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_prj\REQM\DOC\XCSS_SIZEING\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -15,8 +15,8 @@
     <sheet name="표지" sheetId="13" r:id="rId1"/>
     <sheet name="문서이력" sheetId="1" r:id="rId2"/>
     <sheet name="방안" sheetId="2" r:id="rId3"/>
-    <sheet name="결론" sheetId="3" r:id="rId4"/>
-    <sheet name="회의록" sheetId="4" r:id="rId5"/>
+    <sheet name="회의록" sheetId="4" r:id="rId4"/>
+    <sheet name="결론" sheetId="3" r:id="rId5"/>
     <sheet name="CSS속성.현황" sheetId="5" r:id="rId6"/>
     <sheet name="컴포넌트별 점검" sheetId="6" r:id="rId7"/>
     <sheet name="확장속성.최종" sheetId="7" r:id="rId8"/>
@@ -5554,6 +5554,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5568,11 +5573,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5618,16 +5618,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="34" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="44" fillId="14" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="24" fillId="12" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5641,47 +5641,53 @@
     <xf numFmtId="0" fontId="50" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="47" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="55" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="57" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="66" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -5692,13 +5698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="30" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -7251,20 +7251,20 @@
   <sheetData>
     <row r="1" spans="2:4" ht="6" customHeight="1"/>
     <row r="2" spans="2:4" ht="21.95" customHeight="1">
-      <c r="B2" s="251" t="s">
+      <c r="B2" s="253" t="s">
         <v>397</v>
       </c>
       <c r="C2" s="244"/>
     </row>
     <row r="3" spans="2:4" ht="6" customHeight="1"/>
     <row r="4" spans="2:4" ht="18" customHeight="1">
-      <c r="B4" s="250" t="s">
+      <c r="B4" s="247" t="s">
         <v>398</v>
       </c>
       <c r="C4" s="244"/>
     </row>
     <row r="5" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B5" s="247" t="s">
+      <c r="B5" s="250" t="s">
         <v>399</v>
       </c>
       <c r="C5" s="244"/>
@@ -7292,7 +7292,7 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B13" s="247" t="s">
+      <c r="B13" s="250" t="s">
         <v>404</v>
       </c>
       <c r="C13" s="244"/>
@@ -7304,7 +7304,7 @@
       <c r="C14" s="244"/>
     </row>
     <row r="15" spans="2:4" ht="15.95" customHeight="1">
-      <c r="B15" s="247" t="s">
+      <c r="B15" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C15" s="244"/>
@@ -7334,44 +7334,44 @@
       <c r="C19" s="244"/>
     </row>
     <row r="20" spans="2:3" ht="15" customHeight="1">
-      <c r="B20" s="253" t="s">
+      <c r="B20" s="252" t="s">
         <v>411</v>
       </c>
       <c r="C20" s="244"/>
     </row>
     <row r="21" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B21" s="248" t="s">
+      <c r="B21" s="251" t="s">
         <v>412</v>
       </c>
       <c r="C21" s="244"/>
     </row>
     <row r="22" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B22" s="248" t="s">
+      <c r="B22" s="251" t="s">
         <v>413</v>
       </c>
       <c r="C22" s="244"/>
     </row>
     <row r="23" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B23" s="248" t="s">
+      <c r="B23" s="251" t="s">
         <v>414</v>
       </c>
       <c r="C23" s="244"/>
     </row>
     <row r="24" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B24" s="248" t="s">
+      <c r="B24" s="251" t="s">
         <v>415</v>
       </c>
       <c r="C24" s="244"/>
     </row>
     <row r="25" spans="2:3" ht="6" customHeight="1"/>
     <row r="26" spans="2:3" ht="18" customHeight="1">
-      <c r="B26" s="250" t="s">
+      <c r="B26" s="247" t="s">
         <v>416</v>
       </c>
       <c r="C26" s="244"/>
     </row>
     <row r="27" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B27" s="247" t="s">
+      <c r="B27" s="250" t="s">
         <v>399</v>
       </c>
       <c r="C27" s="244"/>
@@ -7440,7 +7440,7 @@
       <c r="B46" s="159"/>
     </row>
     <row r="47" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B47" s="247" t="s">
+      <c r="B47" s="250" t="s">
         <v>419</v>
       </c>
       <c r="C47" s="244"/>
@@ -7458,7 +7458,7 @@
       <c r="C49" s="244"/>
     </row>
     <row r="50" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B50" s="247" t="s">
+      <c r="B50" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C50" s="244"/>
@@ -7477,13 +7477,13 @@
     </row>
     <row r="53" spans="2:3" ht="6" customHeight="1"/>
     <row r="54" spans="2:3" ht="18" customHeight="1">
-      <c r="B54" s="250" t="s">
+      <c r="B54" s="247" t="s">
         <v>424</v>
       </c>
       <c r="C54" s="244"/>
     </row>
     <row r="55" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B55" s="247" t="s">
+      <c r="B55" s="250" t="s">
         <v>425</v>
       </c>
       <c r="C55" s="244"/>
@@ -7495,7 +7495,7 @@
       <c r="C56" s="244"/>
     </row>
     <row r="57" spans="2:3" ht="14.1" customHeight="1">
-      <c r="B57" s="252" t="s">
+      <c r="B57" s="248" t="s">
         <v>427</v>
       </c>
       <c r="C57" s="244"/>
@@ -7504,7 +7504,7 @@
       <c r="B58" s="161"/>
     </row>
     <row r="59" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B59" s="247" t="s">
+      <c r="B59" s="250" t="s">
         <v>428</v>
       </c>
       <c r="C59" s="244"/>
@@ -7582,7 +7582,7 @@
       <c r="B80" s="159"/>
     </row>
     <row r="81" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B81" s="247" t="s">
+      <c r="B81" s="250" t="s">
         <v>404</v>
       </c>
       <c r="C81" s="244"/>
@@ -7594,7 +7594,7 @@
       <c r="C82" s="244"/>
     </row>
     <row r="83" spans="2:3" ht="15.95" customHeight="1">
-      <c r="B83" s="247" t="s">
+      <c r="B83" s="250" t="s">
         <v>406</v>
       </c>
       <c r="C83" s="244"/>
@@ -7614,7 +7614,7 @@
     <row r="86" spans="2:3" ht="6" customHeight="1"/>
     <row r="87" spans="2:3" ht="6" customHeight="1"/>
     <row r="88" spans="2:3" ht="18" customHeight="1">
-      <c r="B88" s="250" t="s">
+      <c r="B88" s="247" t="s">
         <v>435</v>
       </c>
       <c r="C88" s="244"/>
@@ -7663,6 +7663,30 @@
     <row r="95" spans="2:3" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
     <mergeCell ref="B88:C88"/>
     <mergeCell ref="B57:C57"/>
     <mergeCell ref="B82:C82"/>
@@ -7679,30 +7703,6 @@
     <mergeCell ref="B51:C51"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B59:C59"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7725,7 +7725,7 @@
   <sheetData>
     <row r="1" spans="2:5" ht="6" customHeight="1"/>
     <row r="2" spans="2:5" ht="24" customHeight="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="258" t="s">
         <v>440</v>
       </c>
       <c r="C2" s="244"/>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="3" spans="2:5" ht="6" customHeight="1"/>
     <row r="4" spans="2:5" ht="18" customHeight="1">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="254" t="s">
         <v>441</v>
       </c>
       <c r="C4" s="244"/>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="18" spans="2:5" ht="6" customHeight="1"/>
     <row r="19" spans="2:5" ht="18" customHeight="1">
-      <c r="B19" s="258" t="s">
+      <c r="B19" s="254" t="s">
         <v>474</v>
       </c>
       <c r="C19" s="244"/>
@@ -7914,7 +7914,7 @@
       <c r="E19" s="244"/>
     </row>
     <row r="20" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B20" s="259" t="s">
+      <c r="B20" s="255" t="s">
         <v>475</v>
       </c>
       <c r="C20" s="244"/>
@@ -7922,7 +7922,7 @@
       <c r="E20" s="244"/>
     </row>
     <row r="21" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B21" s="255" t="s">
+      <c r="B21" s="259" t="s">
         <v>476</v>
       </c>
       <c r="C21" s="244"/>
@@ -7930,7 +7930,7 @@
       <c r="E21" s="244"/>
     </row>
     <row r="22" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B22" s="254" t="s">
+      <c r="B22" s="256" t="s">
         <v>477</v>
       </c>
       <c r="C22" s="244"/>
@@ -7938,7 +7938,7 @@
       <c r="E22" s="244"/>
     </row>
     <row r="23" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B23" s="254" t="s">
+      <c r="B23" s="256" t="s">
         <v>478</v>
       </c>
       <c r="C23" s="244"/>
@@ -7946,7 +7946,7 @@
       <c r="E23" s="244"/>
     </row>
     <row r="24" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B24" s="254" t="s">
+      <c r="B24" s="256" t="s">
         <v>479</v>
       </c>
       <c r="C24" s="244"/>
@@ -7954,7 +7954,7 @@
       <c r="E24" s="244"/>
     </row>
     <row r="25" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B25" s="254" t="s">
+      <c r="B25" s="256" t="s">
         <v>480</v>
       </c>
       <c r="C25" s="244"/>
@@ -7962,7 +7962,7 @@
       <c r="E25" s="244"/>
     </row>
     <row r="26" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B26" s="254" t="s">
+      <c r="B26" s="256" t="s">
         <v>481</v>
       </c>
       <c r="C26" s="244"/>
@@ -7971,7 +7971,7 @@
     </row>
     <row r="27" spans="2:5" ht="6" customHeight="1"/>
     <row r="28" spans="2:5" ht="18" customHeight="1">
-      <c r="B28" s="258" t="s">
+      <c r="B28" s="254" t="s">
         <v>482</v>
       </c>
       <c r="C28" s="244"/>
@@ -7979,7 +7979,7 @@
       <c r="E28" s="244"/>
     </row>
     <row r="29" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B29" s="259" t="s">
+      <c r="B29" s="255" t="s">
         <v>483</v>
       </c>
       <c r="C29" s="244"/>
@@ -7987,7 +7987,7 @@
       <c r="E29" s="244"/>
     </row>
     <row r="30" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B30" s="255" t="s">
+      <c r="B30" s="259" t="s">
         <v>476</v>
       </c>
       <c r="C30" s="244"/>
@@ -7995,7 +7995,7 @@
       <c r="E30" s="244"/>
     </row>
     <row r="31" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B31" s="254" t="s">
+      <c r="B31" s="256" t="s">
         <v>484</v>
       </c>
       <c r="C31" s="244"/>
@@ -8003,7 +8003,7 @@
       <c r="E31" s="244"/>
     </row>
     <row r="32" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B32" s="254" t="s">
+      <c r="B32" s="256" t="s">
         <v>485</v>
       </c>
       <c r="C32" s="244"/>
@@ -8011,7 +8011,7 @@
       <c r="E32" s="244"/>
     </row>
     <row r="33" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B33" s="254" t="s">
+      <c r="B33" s="256" t="s">
         <v>486</v>
       </c>
       <c r="C33" s="244"/>
@@ -8019,7 +8019,7 @@
       <c r="E33" s="244"/>
     </row>
     <row r="34" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B34" s="254" t="s">
+      <c r="B34" s="256" t="s">
         <v>487</v>
       </c>
       <c r="C34" s="244"/>
@@ -8027,7 +8027,7 @@
       <c r="E34" s="244"/>
     </row>
     <row r="35" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B35" s="254" t="s">
+      <c r="B35" s="256" t="s">
         <v>481</v>
       </c>
       <c r="C35" s="244"/>
@@ -8036,7 +8036,7 @@
     </row>
     <row r="36" spans="2:5" ht="6" customHeight="1"/>
     <row r="37" spans="2:5" ht="18" customHeight="1">
-      <c r="B37" s="258" t="s">
+      <c r="B37" s="254" t="s">
         <v>488</v>
       </c>
       <c r="C37" s="244"/>
@@ -8044,7 +8044,7 @@
       <c r="E37" s="244"/>
     </row>
     <row r="38" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B38" s="256" t="s">
+      <c r="B38" s="260" t="s">
         <v>489</v>
       </c>
       <c r="C38" s="244"/>
@@ -8052,7 +8052,7 @@
       <c r="E38" s="244"/>
     </row>
     <row r="39" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B39" s="255" t="s">
+      <c r="B39" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C39" s="244"/>
@@ -8060,7 +8060,7 @@
       <c r="E39" s="244"/>
     </row>
     <row r="40" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B40" s="254" t="s">
+      <c r="B40" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C40" s="244"/>
@@ -8068,7 +8068,7 @@
       <c r="E40" s="244"/>
     </row>
     <row r="41" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B41" s="254" t="s">
+      <c r="B41" s="256" t="s">
         <v>492</v>
       </c>
       <c r="C41" s="244"/>
@@ -8076,7 +8076,7 @@
       <c r="E41" s="244"/>
     </row>
     <row r="42" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B42" s="254" t="s">
+      <c r="B42" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C42" s="244"/>
@@ -8084,7 +8084,7 @@
       <c r="E42" s="244"/>
     </row>
     <row r="43" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B43" s="254" t="s">
+      <c r="B43" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C43" s="244"/>
@@ -8092,7 +8092,7 @@
       <c r="E43" s="244"/>
     </row>
     <row r="44" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B44" s="254" t="s">
+      <c r="B44" s="256" t="s">
         <v>495</v>
       </c>
       <c r="C44" s="244"/>
@@ -8117,7 +8117,7 @@
     </row>
     <row r="47" spans="2:5" ht="6" customHeight="1"/>
     <row r="48" spans="2:5" ht="18" customHeight="1">
-      <c r="B48" s="258" t="s">
+      <c r="B48" s="254" t="s">
         <v>498</v>
       </c>
       <c r="C48" s="244"/>
@@ -8125,7 +8125,7 @@
       <c r="E48" s="244"/>
     </row>
     <row r="49" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B49" s="256" t="s">
+      <c r="B49" s="260" t="s">
         <v>499</v>
       </c>
       <c r="C49" s="244"/>
@@ -8133,7 +8133,7 @@
       <c r="E49" s="244"/>
     </row>
     <row r="50" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B50" s="255" t="s">
+      <c r="B50" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C50" s="244"/>
@@ -8141,7 +8141,7 @@
       <c r="E50" s="244"/>
     </row>
     <row r="51" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B51" s="254" t="s">
+      <c r="B51" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C51" s="244"/>
@@ -8149,7 +8149,7 @@
       <c r="E51" s="244"/>
     </row>
     <row r="52" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B52" s="254" t="s">
+      <c r="B52" s="256" t="s">
         <v>500</v>
       </c>
       <c r="C52" s="244"/>
@@ -8157,7 +8157,7 @@
       <c r="E52" s="244"/>
     </row>
     <row r="53" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B53" s="254" t="s">
+      <c r="B53" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C53" s="244"/>
@@ -8165,7 +8165,7 @@
       <c r="E53" s="244"/>
     </row>
     <row r="54" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B54" s="254" t="s">
+      <c r="B54" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C54" s="244"/>
@@ -8173,7 +8173,7 @@
       <c r="E54" s="244"/>
     </row>
     <row r="55" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B55" s="254" t="s">
+      <c r="B55" s="256" t="s">
         <v>501</v>
       </c>
       <c r="C55" s="244"/>
@@ -8198,7 +8198,7 @@
     </row>
     <row r="58" spans="2:5" ht="6" customHeight="1"/>
     <row r="59" spans="2:5" ht="18" customHeight="1">
-      <c r="B59" s="258" t="s">
+      <c r="B59" s="254" t="s">
         <v>503</v>
       </c>
       <c r="C59" s="244"/>
@@ -8206,7 +8206,7 @@
       <c r="E59" s="244"/>
     </row>
     <row r="60" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B60" s="259" t="s">
+      <c r="B60" s="255" t="s">
         <v>504</v>
       </c>
       <c r="C60" s="244"/>
@@ -8630,7 +8630,7 @@
     </row>
     <row r="92" spans="2:5" ht="6" customHeight="1"/>
     <row r="93" spans="2:5" ht="18" customHeight="1">
-      <c r="B93" s="258" t="s">
+      <c r="B93" s="254" t="s">
         <v>519</v>
       </c>
       <c r="C93" s="244"/>
@@ -8638,7 +8638,7 @@
       <c r="E93" s="244"/>
     </row>
     <row r="94" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B94" s="259" t="s">
+      <c r="B94" s="255" t="s">
         <v>520</v>
       </c>
       <c r="C94" s="244"/>
@@ -8646,7 +8646,7 @@
       <c r="E94" s="244"/>
     </row>
     <row r="95" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B95" s="255" t="s">
+      <c r="B95" s="259" t="s">
         <v>521</v>
       </c>
       <c r="C95" s="244"/>
@@ -8654,7 +8654,7 @@
       <c r="E95" s="244"/>
     </row>
     <row r="96" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B96" s="254" t="s">
+      <c r="B96" s="256" t="s">
         <v>522</v>
       </c>
       <c r="C96" s="244"/>
@@ -8662,7 +8662,7 @@
       <c r="E96" s="244"/>
     </row>
     <row r="97" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B97" s="254" t="s">
+      <c r="B97" s="256" t="s">
         <v>523</v>
       </c>
       <c r="C97" s="244"/>
@@ -8670,7 +8670,7 @@
       <c r="E97" s="244"/>
     </row>
     <row r="98" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B98" s="254" t="s">
+      <c r="B98" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C98" s="244"/>
@@ -8678,7 +8678,7 @@
       <c r="E98" s="244"/>
     </row>
     <row r="99" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B99" s="254" t="s">
+      <c r="B99" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C99" s="244"/>
@@ -8686,7 +8686,7 @@
       <c r="E99" s="244"/>
     </row>
     <row r="100" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B100" s="254" t="s">
+      <c r="B100" s="256" t="s">
         <v>524</v>
       </c>
       <c r="C100" s="244"/>
@@ -8694,7 +8694,7 @@
       <c r="E100" s="244"/>
     </row>
     <row r="101" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B101" s="255" t="s">
+      <c r="B101" s="259" t="s">
         <v>525</v>
       </c>
       <c r="C101" s="244"/>
@@ -8719,7 +8719,7 @@
     </row>
     <row r="104" spans="2:5" ht="6" customHeight="1"/>
     <row r="105" spans="2:5" ht="18" customHeight="1">
-      <c r="B105" s="258" t="s">
+      <c r="B105" s="254" t="s">
         <v>528</v>
       </c>
       <c r="C105" s="244"/>
@@ -8727,7 +8727,7 @@
       <c r="E105" s="244"/>
     </row>
     <row r="106" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B106" s="259" t="s">
+      <c r="B106" s="255" t="s">
         <v>529</v>
       </c>
       <c r="C106" s="244"/>
@@ -8743,7 +8743,7 @@
       <c r="E107" s="244"/>
     </row>
     <row r="108" spans="2:5" ht="15.95" customHeight="1">
-      <c r="B108" s="255" t="s">
+      <c r="B108" s="259" t="s">
         <v>490</v>
       </c>
       <c r="C108" s="244"/>
@@ -8751,7 +8751,7 @@
       <c r="E108" s="244"/>
     </row>
     <row r="109" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B109" s="254" t="s">
+      <c r="B109" s="256" t="s">
         <v>491</v>
       </c>
       <c r="C109" s="244"/>
@@ -8759,7 +8759,7 @@
       <c r="E109" s="244"/>
     </row>
     <row r="110" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B110" s="254" t="s">
+      <c r="B110" s="256" t="s">
         <v>531</v>
       </c>
       <c r="C110" s="244"/>
@@ -8767,7 +8767,7 @@
       <c r="E110" s="244"/>
     </row>
     <row r="111" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B111" s="254" t="s">
+      <c r="B111" s="256" t="s">
         <v>493</v>
       </c>
       <c r="C111" s="244"/>
@@ -8775,7 +8775,7 @@
       <c r="E111" s="244"/>
     </row>
     <row r="112" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B112" s="254" t="s">
+      <c r="B112" s="256" t="s">
         <v>494</v>
       </c>
       <c r="C112" s="244"/>
@@ -8783,7 +8783,7 @@
       <c r="E112" s="244"/>
     </row>
     <row r="113" spans="2:5" ht="14.1" customHeight="1">
-      <c r="B113" s="254" t="s">
+      <c r="B113" s="256" t="s">
         <v>532</v>
       </c>
       <c r="C113" s="244"/>
@@ -8793,7 +8793,7 @@
     <row r="114" spans="2:5" ht="6" customHeight="1"/>
     <row r="115" spans="2:5" ht="6" customHeight="1"/>
     <row r="116" spans="2:5" ht="18" customHeight="1">
-      <c r="B116" s="258" t="s">
+      <c r="B116" s="254" t="s">
         <v>533</v>
       </c>
       <c r="C116" s="244"/>
@@ -8930,6 +8930,53 @@
     <row r="127" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="63">
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B55:E55"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="B105:E105"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B110:E110"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B106:E106"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B5:E5"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B51:E51"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B111:E111"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B107:E107"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B61:E61"/>
+    <mergeCell ref="B57:E57"/>
+    <mergeCell ref="B53:E53"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B100:E100"/>
     <mergeCell ref="B116:E116"/>
     <mergeCell ref="B29:E29"/>
     <mergeCell ref="B112:E112"/>
@@ -8946,53 +8993,6 @@
     <mergeCell ref="B46:E46"/>
     <mergeCell ref="B93:E93"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="B111:E111"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B107:E107"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B50:E50"/>
-    <mergeCell ref="B106:E106"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B39:E39"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="B105:E105"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B45:E45"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9015,7 +9015,7 @@
   <sheetData>
     <row r="1" spans="2:14" ht="6" customHeight="1"/>
     <row r="2" spans="2:14" ht="24" customHeight="1">
-      <c r="B2" s="260" t="s">
+      <c r="B2" s="258" t="s">
         <v>712</v>
       </c>
       <c r="C2" s="244"/>
@@ -9025,7 +9025,7 @@
     </row>
     <row r="3" spans="2:14" ht="6" customHeight="1"/>
     <row r="4" spans="2:14" ht="18" customHeight="1">
-      <c r="B4" s="258" t="s">
+      <c r="B4" s="254" t="s">
         <v>557</v>
       </c>
       <c r="C4" s="244"/>
@@ -9034,7 +9034,7 @@
       <c r="F4" s="244"/>
     </row>
     <row r="5" spans="2:14" ht="14.1" customHeight="1">
-      <c r="B5" s="266" t="s">
+      <c r="B5" s="262" t="s">
         <v>716</v>
       </c>
       <c r="C5" s="244"/>
@@ -9172,7 +9172,7 @@
       <c r="N13" s="160"/>
     </row>
     <row r="14" spans="2:14" ht="18" customHeight="1">
-      <c r="B14" s="258" t="s">
+      <c r="B14" s="254" t="s">
         <v>575</v>
       </c>
       <c r="C14" s="244"/>
@@ -9188,7 +9188,7 @@
       <c r="N14" s="160"/>
     </row>
     <row r="15" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B15" s="255" t="s">
+      <c r="B15" s="259" t="s">
         <v>576</v>
       </c>
       <c r="C15" s="244"/>
@@ -9220,7 +9220,7 @@
       <c r="N16" s="160"/>
     </row>
     <row r="17" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B17" s="261" t="s">
+      <c r="B17" s="263" t="s">
         <v>722</v>
       </c>
       <c r="C17" s="244"/>
@@ -9236,7 +9236,7 @@
       <c r="N17" s="160"/>
     </row>
     <row r="18" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B18" s="261" t="s">
+      <c r="B18" s="263" t="s">
         <v>717</v>
       </c>
       <c r="C18" s="244"/>
@@ -9252,7 +9252,7 @@
       <c r="N18" s="160"/>
     </row>
     <row r="19" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B19" s="261" t="s">
+      <c r="B19" s="263" t="s">
         <v>718</v>
       </c>
       <c r="C19" s="244"/>
@@ -9261,7 +9261,7 @@
       <c r="F19" s="244"/>
     </row>
     <row r="20" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B20" s="254" t="s">
+      <c r="B20" s="256" t="s">
         <v>578</v>
       </c>
       <c r="C20" s="244"/>
@@ -9270,7 +9270,7 @@
       <c r="F20" s="244"/>
     </row>
     <row r="21" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B21" s="261" t="s">
+      <c r="B21" s="263" t="s">
         <v>719</v>
       </c>
       <c r="C21" s="244"/>
@@ -9279,7 +9279,7 @@
       <c r="F21" s="244"/>
     </row>
     <row r="22" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B22" s="261" t="s">
+      <c r="B22" s="263" t="s">
         <v>721</v>
       </c>
       <c r="C22" s="244"/>
@@ -9288,7 +9288,7 @@
       <c r="F22" s="244"/>
     </row>
     <row r="23" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B23" s="261" t="s">
+      <c r="B23" s="263" t="s">
         <v>720</v>
       </c>
       <c r="C23" s="244"/>
@@ -9297,7 +9297,7 @@
       <c r="F23" s="244"/>
     </row>
     <row r="24" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B24" s="254" t="s">
+      <c r="B24" s="256" t="s">
         <v>579</v>
       </c>
       <c r="C24" s="244"/>
@@ -9306,7 +9306,7 @@
       <c r="F24" s="244"/>
     </row>
     <row r="25" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B25" s="255" t="s">
+      <c r="B25" s="259" t="s">
         <v>580</v>
       </c>
       <c r="C25" s="244"/>
@@ -9324,7 +9324,7 @@
       <c r="F26" s="244"/>
     </row>
     <row r="27" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B27" s="254" t="s">
+      <c r="B27" s="256" t="s">
         <v>582</v>
       </c>
       <c r="C27" s="244"/>
@@ -9333,7 +9333,7 @@
       <c r="F27" s="244"/>
     </row>
     <row r="28" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B28" s="254" t="s">
+      <c r="B28" s="256" t="s">
         <v>583</v>
       </c>
       <c r="C28" s="244"/>
@@ -9342,7 +9342,7 @@
       <c r="F28" s="244"/>
     </row>
     <row r="29" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B29" s="254" t="s">
+      <c r="B29" s="256" t="s">
         <v>584</v>
       </c>
       <c r="C29" s="244"/>
@@ -9351,7 +9351,7 @@
       <c r="F29" s="244"/>
     </row>
     <row r="30" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B30" s="254" t="s">
+      <c r="B30" s="256" t="s">
         <v>585</v>
       </c>
       <c r="C30" s="244"/>
@@ -9360,7 +9360,7 @@
       <c r="F30" s="244"/>
     </row>
     <row r="31" spans="2:14" ht="12.95" customHeight="1">
-      <c r="B31" s="254" t="s">
+      <c r="B31" s="256" t="s">
         <v>586</v>
       </c>
       <c r="C31" s="244"/>
@@ -9369,7 +9369,7 @@
       <c r="F31" s="244"/>
     </row>
     <row r="32" spans="2:14" ht="15.95" customHeight="1">
-      <c r="B32" s="255" t="s">
+      <c r="B32" s="259" t="s">
         <v>587</v>
       </c>
       <c r="C32" s="244"/>
@@ -9387,7 +9387,7 @@
       <c r="F33" s="244"/>
     </row>
     <row r="34" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B34" s="254" t="s">
+      <c r="B34" s="256" t="s">
         <v>589</v>
       </c>
       <c r="C34" s="244"/>
@@ -9396,16 +9396,16 @@
       <c r="F34" s="244"/>
     </row>
     <row r="35" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B35" s="262" t="s">
+      <c r="B35" s="264" t="s">
         <v>723</v>
       </c>
-      <c r="C35" s="263"/>
-      <c r="D35" s="263"/>
-      <c r="E35" s="263"/>
-      <c r="F35" s="263"/>
+      <c r="C35" s="265"/>
+      <c r="D35" s="265"/>
+      <c r="E35" s="265"/>
+      <c r="F35" s="265"/>
     </row>
     <row r="36" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B36" s="254" t="s">
+      <c r="B36" s="256" t="s">
         <v>590</v>
       </c>
       <c r="C36" s="244"/>
@@ -9414,7 +9414,7 @@
       <c r="F36" s="244"/>
     </row>
     <row r="37" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B37" s="254" t="s">
+      <c r="B37" s="256" t="s">
         <v>591</v>
       </c>
       <c r="C37" s="244"/>
@@ -9423,7 +9423,7 @@
       <c r="F37" s="244"/>
     </row>
     <row r="38" spans="2:6" ht="12.95" customHeight="1">
-      <c r="B38" s="254" t="s">
+      <c r="B38" s="256" t="s">
         <v>592</v>
       </c>
       <c r="C38" s="244"/>
@@ -9433,7 +9433,7 @@
     </row>
     <row r="39" spans="2:6" ht="6" customHeight="1"/>
     <row r="40" spans="2:6" ht="18" customHeight="1">
-      <c r="B40" s="258" t="s">
+      <c r="B40" s="254" t="s">
         <v>593</v>
       </c>
       <c r="C40" s="244"/>
@@ -9442,7 +9442,7 @@
       <c r="F40" s="244"/>
     </row>
     <row r="41" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B41" s="265" t="s">
+      <c r="B41" s="266" t="s">
         <v>594</v>
       </c>
       <c r="C41" s="244"/>
@@ -9469,7 +9469,7 @@
       </c>
     </row>
     <row r="44" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B44" s="264" t="s">
+      <c r="B44" s="261" t="s">
         <v>600</v>
       </c>
       <c r="C44" s="244"/>
@@ -9568,7 +9568,7 @@
       <c r="F50" s="164"/>
     </row>
     <row r="51" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B51" s="264" t="s">
+      <c r="B51" s="261" t="s">
         <v>619</v>
       </c>
       <c r="C51" s="244"/>
@@ -9637,7 +9637,7 @@
       <c r="F55" s="171"/>
     </row>
     <row r="56" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B56" s="264" t="s">
+      <c r="B56" s="261" t="s">
         <v>629</v>
       </c>
       <c r="C56" s="244"/>
@@ -9691,7 +9691,7 @@
       <c r="F59" s="171"/>
     </row>
     <row r="60" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B60" s="264" t="s">
+      <c r="B60" s="261" t="s">
         <v>637</v>
       </c>
       <c r="C60" s="244"/>
@@ -9760,7 +9760,7 @@
       <c r="F64" s="164"/>
     </row>
     <row r="65" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B65" s="264" t="s">
+      <c r="B65" s="261" t="s">
         <v>646</v>
       </c>
       <c r="C65" s="244"/>
@@ -9814,7 +9814,7 @@
       <c r="F68" s="164"/>
     </row>
     <row r="69" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B69" s="264" t="s">
+      <c r="B69" s="261" t="s">
         <v>655</v>
       </c>
       <c r="C69" s="244"/>
@@ -9868,7 +9868,7 @@
       <c r="F72" s="164"/>
     </row>
     <row r="73" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B73" s="264" t="s">
+      <c r="B73" s="261" t="s">
         <v>661</v>
       </c>
       <c r="C73" s="244"/>
@@ -10042,7 +10042,7 @@
       <c r="F84" s="164"/>
     </row>
     <row r="85" spans="2:6" ht="14.1" customHeight="1">
-      <c r="B85" s="264" t="s">
+      <c r="B85" s="261" t="s">
         <v>680</v>
       </c>
       <c r="C85" s="244"/>
@@ -10082,7 +10082,7 @@
     </row>
     <row r="88" spans="2:6" ht="6" customHeight="1"/>
     <row r="89" spans="2:6" ht="18" customHeight="1">
-      <c r="B89" s="258" t="s">
+      <c r="B89" s="254" t="s">
         <v>688</v>
       </c>
       <c r="C89" s="244"/>
@@ -10188,13 +10188,22 @@
     <row r="98" spans="2:5" ht="6" customHeight="1"/>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="B51:F51"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B17:F17"/>
+    <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B22:F22"/>
+    <mergeCell ref="B28:F28"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B21:F21"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B41:F41"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="B44:F44"/>
     <mergeCell ref="B38:F38"/>
@@ -10211,22 +10220,13 @@
     <mergeCell ref="B31:F31"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B15:F15"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B17:F17"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B35:F35"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B65:F65"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B28:F28"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B60:F60"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B25:F25"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B27:F27"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10266,15 +10266,15 @@
     </row>
     <row r="3" spans="2:10" ht="17.25" customHeight="1">
       <c r="B3" s="4"/>
-      <c r="C3" s="204" t="s">
+      <c r="C3" s="207" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="205"/>
-      <c r="E3" s="205"/>
-      <c r="F3" s="205"/>
-      <c r="G3" s="205"/>
-      <c r="H3" s="205"/>
-      <c r="I3" s="205"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
       <c r="J3" s="5"/>
     </row>
     <row r="4" spans="2:10" ht="15.95" customHeight="1">
@@ -10290,15 +10290,15 @@
     </row>
     <row r="5" spans="2:10" ht="31.5" customHeight="1">
       <c r="B5" s="6"/>
-      <c r="C5" s="206" t="s">
+      <c r="C5" s="209" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="205"/>
-      <c r="E5" s="205"/>
-      <c r="F5" s="205"/>
-      <c r="G5" s="205"/>
-      <c r="H5" s="205"/>
-      <c r="I5" s="205"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
       <c r="J5" s="5"/>
     </row>
     <row r="6" spans="2:10" ht="15.95" customHeight="1">
@@ -10326,11 +10326,11 @@
       <c r="F7" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="207" t="s">
+      <c r="G7" s="210" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="208"/>
-      <c r="I7" s="209"/>
+      <c r="H7" s="211"/>
+      <c r="I7" s="212"/>
       <c r="J7" s="5"/>
     </row>
     <row r="8" spans="2:10" ht="15.95" customHeight="1">
@@ -10715,9 +10715,9 @@
       <c r="D40" s="13"/>
       <c r="E40" s="13"/>
       <c r="F40" s="13"/>
-      <c r="G40" s="210"/>
-      <c r="H40" s="211"/>
-      <c r="I40" s="212"/>
+      <c r="G40" s="204"/>
+      <c r="H40" s="205"/>
+      <c r="I40" s="206"/>
       <c r="J40" s="5"/>
     </row>
     <row r="41" spans="2:10" ht="15.95" customHeight="1">
@@ -10733,6 +10733,26 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="G40:I40"/>
+    <mergeCell ref="G39:I39"/>
+    <mergeCell ref="G38:I38"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="G9:I9"/>
     <mergeCell ref="G12:I12"/>
     <mergeCell ref="G21:I21"/>
@@ -10749,26 +10769,6 @@
     <mergeCell ref="G28:I28"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="G15:I15"/>
-    <mergeCell ref="G40:I40"/>
-    <mergeCell ref="G39:I39"/>
-    <mergeCell ref="G38:I38"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="G7:I7"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
@@ -13980,6 +13980,345 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A3:L50"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="4.625" style="160" customWidth="1"/>
+    <col min="2" max="2" width="4.75" style="160" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:12">
+      <c r="B3" s="78" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12">
+      <c r="B5" s="102" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12">
+      <c r="C6" s="102" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="83"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="83"/>
+    </row>
+    <row r="7" spans="2:12">
+      <c r="C7" s="84" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+    </row>
+    <row r="8" spans="2:12">
+      <c r="C8" s="84" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="83"/>
+      <c r="E8" s="83"/>
+      <c r="F8" s="83"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="83"/>
+      <c r="I8" s="83"/>
+      <c r="J8" s="83"/>
+    </row>
+    <row r="9" spans="2:12">
+      <c r="B9" s="96"/>
+      <c r="C9" s="85" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="83"/>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="83"/>
+    </row>
+    <row r="10" spans="2:12">
+      <c r="B10" s="96"/>
+      <c r="C10" s="84" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="83"/>
+      <c r="E10" s="83"/>
+      <c r="F10" s="83"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="83"/>
+    </row>
+    <row r="11" spans="2:12">
+      <c r="C11" s="84" t="s">
+        <v>170</v>
+      </c>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+    </row>
+    <row r="12" spans="2:12">
+      <c r="C12" s="86" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="83"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="83"/>
+    </row>
+    <row r="13" spans="2:12">
+      <c r="C13" s="86" t="s">
+        <v>172</v>
+      </c>
+      <c r="D13" s="83"/>
+      <c r="E13" s="83"/>
+      <c r="F13" s="83"/>
+      <c r="G13" s="83"/>
+      <c r="H13" s="83"/>
+      <c r="I13" s="83"/>
+      <c r="J13" s="83"/>
+    </row>
+    <row r="14" spans="2:12">
+      <c r="B14" s="96"/>
+      <c r="C14" s="84" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="96"/>
+      <c r="E14" s="83"/>
+      <c r="F14" s="83"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="83"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="83"/>
+      <c r="L14" s="87"/>
+    </row>
+    <row r="15" spans="2:12">
+      <c r="B15" s="96"/>
+      <c r="D15" s="96"/>
+    </row>
+    <row r="16" spans="2:12">
+      <c r="B16" s="102" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="96"/>
+    </row>
+    <row r="17" spans="2:12">
+      <c r="C17" s="96" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="96"/>
+      <c r="L17" s="87"/>
+    </row>
+    <row r="18" spans="2:12">
+      <c r="C18" s="96" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12">
+      <c r="C19" s="96" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12">
+      <c r="C20" s="96" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12">
+      <c r="C21" s="96" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12">
+      <c r="C22" s="96"/>
+    </row>
+    <row r="23" spans="2:12">
+      <c r="C23" s="78" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12">
+      <c r="C24" s="98" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12">
+      <c r="C25" s="86" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12">
+      <c r="C26" s="84" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12">
+      <c r="C27" s="96" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="102"/>
+    </row>
+    <row r="29" spans="2:12">
+      <c r="C29" s="78" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12">
+      <c r="C30" s="96" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" s="96"/>
+      <c r="L30" s="79"/>
+    </row>
+    <row r="31" spans="2:12">
+      <c r="C31" s="98" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" s="96"/>
+    </row>
+    <row r="32" spans="2:12">
+      <c r="C32" s="98" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11">
+      <c r="C33" s="96" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11">
+      <c r="B35" s="85" t="s">
+        <v>188</v>
+      </c>
+      <c r="C35" s="96"/>
+    </row>
+    <row r="36" spans="2:11">
+      <c r="C36" s="99" t="s">
+        <v>189</v>
+      </c>
+      <c r="D36" s="96"/>
+      <c r="E36" s="96"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="96"/>
+      <c r="K36" s="96"/>
+    </row>
+    <row r="37" spans="2:11">
+      <c r="C37" s="81" t="s">
+        <v>190</v>
+      </c>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="154"/>
+    </row>
+    <row r="38" spans="2:11">
+      <c r="C38" s="81" t="s">
+        <v>191</v>
+      </c>
+      <c r="E38" s="81"/>
+    </row>
+    <row r="39" spans="2:11">
+      <c r="C39" s="81"/>
+      <c r="E39" s="81"/>
+    </row>
+    <row r="40" spans="2:11">
+      <c r="C40" s="82" t="s">
+        <v>192</v>
+      </c>
+      <c r="D40" s="154"/>
+      <c r="E40" s="154"/>
+    </row>
+    <row r="41" spans="2:11">
+      <c r="C41" s="86" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11">
+      <c r="C42" s="84" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11">
+      <c r="C43" s="84" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11">
+      <c r="C44" s="82"/>
+      <c r="D44" s="154"/>
+      <c r="E44" s="154"/>
+    </row>
+    <row r="45" spans="2:11">
+      <c r="B45" s="85" t="s">
+        <v>157</v>
+      </c>
+      <c r="C45" s="96"/>
+      <c r="D45" s="154"/>
+      <c r="E45" s="154"/>
+    </row>
+    <row r="46" spans="2:11">
+      <c r="C46" s="96" t="s">
+        <v>196</v>
+      </c>
+      <c r="D46" s="154"/>
+      <c r="E46" s="154"/>
+    </row>
+    <row r="47" spans="2:11">
+      <c r="C47" s="96" t="s">
+        <v>159</v>
+      </c>
+      <c r="D47" s="96"/>
+      <c r="E47" s="154"/>
+    </row>
+    <row r="48" spans="2:11">
+      <c r="C48" s="96" t="s">
+        <v>197</v>
+      </c>
+      <c r="D48" s="96"/>
+      <c r="E48" s="154"/>
+    </row>
+    <row r="49" spans="3:5">
+      <c r="C49" s="96" t="s">
+        <v>198</v>
+      </c>
+      <c r="D49" s="96"/>
+      <c r="E49" s="154"/>
+    </row>
+    <row r="50" spans="3:5">
+      <c r="C50" s="96" t="s">
+        <v>199</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="37" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A2:AG59"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
@@ -14922,345 +15261,6 @@
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A3:L50"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
-  <cols>
-    <col min="1" max="1" width="4.625" style="160" customWidth="1"/>
-    <col min="2" max="2" width="4.75" style="160" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:12">
-      <c r="B3" s="78" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="102" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="C6" s="102" t="s">
-        <v>165</v>
-      </c>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="C7" s="84" t="s">
-        <v>166</v>
-      </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="C8" s="84" t="s">
-        <v>167</v>
-      </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="96"/>
-      <c r="C9" s="85" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="96"/>
-      <c r="C10" s="84" t="s">
-        <v>169</v>
-      </c>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
-    </row>
-    <row r="11" spans="2:12">
-      <c r="C11" s="84" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-    </row>
-    <row r="12" spans="2:12">
-      <c r="C12" s="86" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-    </row>
-    <row r="13" spans="2:12">
-      <c r="C13" s="86" t="s">
-        <v>172</v>
-      </c>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-    </row>
-    <row r="14" spans="2:12">
-      <c r="B14" s="96"/>
-      <c r="C14" s="84" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="96"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="L14" s="87"/>
-    </row>
-    <row r="15" spans="2:12">
-      <c r="B15" s="96"/>
-      <c r="D15" s="96"/>
-    </row>
-    <row r="16" spans="2:12">
-      <c r="B16" s="102" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="96"/>
-    </row>
-    <row r="17" spans="2:12">
-      <c r="C17" s="96" t="s">
-        <v>175</v>
-      </c>
-      <c r="D17" s="96"/>
-      <c r="L17" s="87"/>
-    </row>
-    <row r="18" spans="2:12">
-      <c r="C18" s="96" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="19" spans="2:12">
-      <c r="C19" s="96" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12">
-      <c r="C20" s="96" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="21" spans="2:12">
-      <c r="C21" s="96" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="22" spans="2:12">
-      <c r="C22" s="96"/>
-    </row>
-    <row r="23" spans="2:12">
-      <c r="C23" s="78" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="2:12">
-      <c r="C24" s="98" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="2:12">
-      <c r="C25" s="86" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="26" spans="2:12">
-      <c r="C26" s="84" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="27" spans="2:12">
-      <c r="C27" s="96" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="102"/>
-    </row>
-    <row r="29" spans="2:12">
-      <c r="C29" s="78" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="2:12">
-      <c r="C30" s="96" t="s">
-        <v>184</v>
-      </c>
-      <c r="D30" s="96"/>
-      <c r="L30" s="79"/>
-    </row>
-    <row r="31" spans="2:12">
-      <c r="C31" s="98" t="s">
-        <v>185</v>
-      </c>
-      <c r="D31" s="96"/>
-    </row>
-    <row r="32" spans="2:12">
-      <c r="C32" s="98" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="33" spans="2:11">
-      <c r="C33" s="96" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="2:11">
-      <c r="B35" s="85" t="s">
-        <v>188</v>
-      </c>
-      <c r="C35" s="96"/>
-    </row>
-    <row r="36" spans="2:11">
-      <c r="C36" s="99" t="s">
-        <v>189</v>
-      </c>
-      <c r="D36" s="96"/>
-      <c r="E36" s="96"/>
-      <c r="F36" s="96"/>
-      <c r="G36" s="96"/>
-      <c r="H36" s="96"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="96"/>
-      <c r="K36" s="96"/>
-    </row>
-    <row r="37" spans="2:11">
-      <c r="C37" s="81" t="s">
-        <v>190</v>
-      </c>
-      <c r="D37" s="80"/>
-      <c r="E37" s="80"/>
-      <c r="F37" s="154"/>
-    </row>
-    <row r="38" spans="2:11">
-      <c r="C38" s="81" t="s">
-        <v>191</v>
-      </c>
-      <c r="E38" s="81"/>
-    </row>
-    <row r="39" spans="2:11">
-      <c r="C39" s="81"/>
-      <c r="E39" s="81"/>
-    </row>
-    <row r="40" spans="2:11">
-      <c r="C40" s="82" t="s">
-        <v>192</v>
-      </c>
-      <c r="D40" s="154"/>
-      <c r="E40" s="154"/>
-    </row>
-    <row r="41" spans="2:11">
-      <c r="C41" s="86" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
-      <c r="C42" s="84" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11">
-      <c r="C43" s="84" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
-      <c r="C44" s="82"/>
-      <c r="D44" s="154"/>
-      <c r="E44" s="154"/>
-    </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="85" t="s">
-        <v>157</v>
-      </c>
-      <c r="C45" s="96"/>
-      <c r="D45" s="154"/>
-      <c r="E45" s="154"/>
-    </row>
-    <row r="46" spans="2:11">
-      <c r="C46" s="96" t="s">
-        <v>196</v>
-      </c>
-      <c r="D46" s="154"/>
-      <c r="E46" s="154"/>
-    </row>
-    <row r="47" spans="2:11">
-      <c r="C47" s="96" t="s">
-        <v>159</v>
-      </c>
-      <c r="D47" s="96"/>
-      <c r="E47" s="154"/>
-    </row>
-    <row r="48" spans="2:11">
-      <c r="C48" s="96" t="s">
-        <v>197</v>
-      </c>
-      <c r="D48" s="96"/>
-      <c r="E48" s="154"/>
-    </row>
-    <row r="49" spans="3:5">
-      <c r="C49" s="96" t="s">
-        <v>198</v>
-      </c>
-      <c r="D49" s="96"/>
-      <c r="E49" s="154"/>
-    </row>
-    <row r="50" spans="3:5">
-      <c r="C50" s="96" t="s">
-        <v>199</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="37" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -16844,18 +16844,18 @@
       <c r="L1" s="143"/>
     </row>
     <row r="2" spans="1:12" ht="15.95" hidden="1" customHeight="1">
-      <c r="A2" s="240" t="s">
+      <c r="A2" s="238" t="s">
         <v>279</v>
       </c>
-      <c r="B2" s="241"/>
-      <c r="C2" s="241"/>
-      <c r="D2" s="241"/>
-      <c r="E2" s="241"/>
-      <c r="F2" s="241"/>
-      <c r="G2" s="241"/>
-      <c r="H2" s="241"/>
-      <c r="I2" s="241"/>
-      <c r="J2" s="241"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
     </row>
     <row r="3" spans="1:12" ht="15" hidden="1" customHeight="1">
       <c r="A3" s="92" t="s">
@@ -17019,10 +17019,10 @@
       </c>
       <c r="B9" s="237"/>
       <c r="C9" s="237"/>
-      <c r="D9" s="238"/>
+      <c r="D9" s="240"/>
       <c r="E9" s="237"/>
       <c r="F9" s="237"/>
-      <c r="G9" s="238"/>
+      <c r="G9" s="240"/>
       <c r="H9" s="237"/>
       <c r="I9" s="237"/>
       <c r="J9" s="156"/>
@@ -17491,15 +17491,15 @@
       </c>
     </row>
     <row r="26" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A26" s="239" t="s">
+      <c r="A26" s="241" t="s">
         <v>311</v>
       </c>
       <c r="B26" s="237"/>
       <c r="C26" s="237"/>
-      <c r="D26" s="238"/>
+      <c r="D26" s="240"/>
       <c r="E26" s="237"/>
       <c r="F26" s="237"/>
-      <c r="G26" s="238"/>
+      <c r="G26" s="240"/>
       <c r="H26" s="237"/>
       <c r="I26" s="237"/>
       <c r="J26" s="156"/>
@@ -17799,15 +17799,15 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A38" s="239" t="s">
+      <c r="A38" s="241" t="s">
         <v>324</v>
       </c>
       <c r="B38" s="237"/>
       <c r="C38" s="237"/>
-      <c r="D38" s="238"/>
+      <c r="D38" s="240"/>
       <c r="E38" s="237"/>
       <c r="F38" s="237"/>
-      <c r="G38" s="238"/>
+      <c r="G38" s="240"/>
       <c r="H38" s="237"/>
       <c r="I38" s="237"/>
       <c r="J38" s="156"/>
@@ -18095,15 +18095,15 @@
       </c>
     </row>
     <row r="49" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A49" s="239" t="s">
+      <c r="A49" s="241" t="s">
         <v>332</v>
       </c>
       <c r="B49" s="237"/>
       <c r="C49" s="237"/>
-      <c r="D49" s="238"/>
+      <c r="D49" s="240"/>
       <c r="E49" s="237"/>
       <c r="F49" s="237"/>
-      <c r="G49" s="238"/>
+      <c r="G49" s="240"/>
       <c r="H49" s="237"/>
       <c r="I49" s="237"/>
       <c r="J49" s="156"/>
@@ -18167,15 +18167,15 @@
       </c>
     </row>
     <row r="52" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A52" s="239" t="s">
+      <c r="A52" s="241" t="s">
         <v>335</v>
       </c>
       <c r="B52" s="237"/>
       <c r="C52" s="237"/>
-      <c r="D52" s="238"/>
+      <c r="D52" s="240"/>
       <c r="E52" s="237"/>
       <c r="F52" s="237"/>
-      <c r="G52" s="238"/>
+      <c r="G52" s="240"/>
       <c r="H52" s="237"/>
       <c r="I52" s="237"/>
       <c r="J52" s="156"/>
@@ -18298,15 +18298,15 @@
       </c>
     </row>
     <row r="57" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A57" s="239" t="s">
+      <c r="A57" s="241" t="s">
         <v>342</v>
       </c>
       <c r="B57" s="237"/>
       <c r="C57" s="237"/>
-      <c r="D57" s="238"/>
+      <c r="D57" s="240"/>
       <c r="E57" s="237"/>
       <c r="F57" s="237"/>
-      <c r="G57" s="238"/>
+      <c r="G57" s="240"/>
       <c r="H57" s="237"/>
       <c r="I57" s="237"/>
       <c r="J57" s="156"/>
@@ -18447,15 +18447,15 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A63" s="239" t="s">
+      <c r="A63" s="241" t="s">
         <v>348</v>
       </c>
       <c r="B63" s="237"/>
       <c r="C63" s="237"/>
-      <c r="D63" s="238"/>
+      <c r="D63" s="240"/>
       <c r="E63" s="237"/>
       <c r="F63" s="237"/>
-      <c r="G63" s="238"/>
+      <c r="G63" s="240"/>
       <c r="H63" s="237"/>
       <c r="I63" s="237"/>
       <c r="J63" s="156"/>
@@ -18488,15 +18488,15 @@
       </c>
     </row>
     <row r="65" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A65" s="239" t="s">
+      <c r="A65" s="241" t="s">
         <v>350</v>
       </c>
       <c r="B65" s="237"/>
       <c r="C65" s="237"/>
-      <c r="D65" s="238"/>
+      <c r="D65" s="240"/>
       <c r="E65" s="237"/>
       <c r="F65" s="237"/>
-      <c r="G65" s="238"/>
+      <c r="G65" s="240"/>
       <c r="H65" s="237"/>
       <c r="I65" s="237"/>
       <c r="J65" s="156"/>
@@ -18583,15 +18583,15 @@
       </c>
     </row>
     <row r="69" spans="1:10" ht="15.95" customHeight="1">
-      <c r="A69" s="239" t="s">
+      <c r="A69" s="241" t="s">
         <v>354</v>
       </c>
       <c r="B69" s="237"/>
       <c r="C69" s="237"/>
-      <c r="D69" s="238"/>
+      <c r="D69" s="240"/>
       <c r="E69" s="237"/>
       <c r="F69" s="237"/>
-      <c r="G69" s="238"/>
+      <c r="G69" s="240"/>
       <c r="H69" s="237"/>
       <c r="I69" s="237"/>
       <c r="J69" s="156"/>
@@ -18706,15 +18706,15 @@
       </c>
     </row>
     <row r="74" spans="1:10">
-      <c r="A74" s="239" t="s">
+      <c r="A74" s="241" t="s">
         <v>359</v>
       </c>
       <c r="B74" s="237"/>
       <c r="C74" s="237"/>
-      <c r="D74" s="238"/>
+      <c r="D74" s="240"/>
       <c r="E74" s="237"/>
       <c r="F74" s="237"/>
-      <c r="G74" s="238"/>
+      <c r="G74" s="240"/>
       <c r="H74" s="237"/>
       <c r="I74" s="237"/>
       <c r="J74" s="156"/>
@@ -18748,21 +18748,6 @@
   </sheetData>
   <autoFilter ref="C1:G75"/>
   <mergeCells count="31">
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="A65:C65"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="A49:C49"/>
     <mergeCell ref="D74:F74"/>
     <mergeCell ref="A38:C38"/>
     <mergeCell ref="A52:C52"/>
@@ -18779,6 +18764,21 @@
     <mergeCell ref="G49:I49"/>
     <mergeCell ref="D52:F52"/>
     <mergeCell ref="G74:I74"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A65:C65"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="A49:C49"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18854,7 +18854,7 @@
       <c r="K2" s="106"/>
     </row>
     <row r="3" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A3" s="238" t="s">
+      <c r="A3" s="240" t="s">
         <v>364</v>
       </c>
       <c r="B3" s="237"/>
@@ -19021,7 +19021,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A8" s="238" t="s">
+      <c r="A8" s="240" t="s">
         <v>370</v>
       </c>
       <c r="B8" s="237"/>
@@ -19071,7 +19071,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A10" s="238" t="s">
+      <c r="A10" s="240" t="s">
         <v>371</v>
       </c>
       <c r="B10" s="237"/>
@@ -19156,7 +19156,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A13" s="238" t="s">
+      <c r="A13" s="240" t="s">
         <v>372</v>
       </c>
       <c r="B13" s="237"/>
@@ -19241,7 +19241,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" ht="16.5" customHeight="1">
-      <c r="A16" s="238" t="s">
+      <c r="A16" s="240" t="s">
         <v>373</v>
       </c>
       <c r="B16" s="237"/>
@@ -19342,7 +19342,7 @@
       <c r="N19" s="144"/>
     </row>
     <row r="20" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A20" s="239" t="s">
+      <c r="A20" s="241" t="s">
         <v>374</v>
       </c>
       <c r="B20" s="237"/>
@@ -19392,7 +19392,7 @@
       </c>
     </row>
     <row r="22" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A22" s="239" t="s">
+      <c r="A22" s="241" t="s">
         <v>279</v>
       </c>
       <c r="B22" s="237"/>
@@ -19827,7 +19827,7 @@
       </c>
     </row>
     <row r="35" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A35" s="239" t="s">
+      <c r="A35" s="241" t="s">
         <v>317</v>
       </c>
       <c r="B35" s="237"/>
@@ -19912,7 +19912,7 @@
       </c>
     </row>
     <row r="38" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A38" s="239" t="s">
+      <c r="A38" s="241" t="s">
         <v>324</v>
       </c>
       <c r="B38" s="237"/>
@@ -20032,7 +20032,7 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A42" s="239" t="s">
+      <c r="A42" s="241" t="s">
         <v>379</v>
       </c>
       <c r="B42" s="237"/>
@@ -20117,7 +20117,7 @@
       </c>
     </row>
     <row r="45" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A45" s="239" t="s">
+      <c r="A45" s="241" t="s">
         <v>335</v>
       </c>
       <c r="B45" s="237"/>
@@ -20272,7 +20272,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A50" s="239" t="s">
+      <c r="A50" s="241" t="s">
         <v>348</v>
       </c>
       <c r="B50" s="237"/>
@@ -20322,7 +20322,7 @@
       </c>
     </row>
     <row r="52" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A52" s="239" t="s">
+      <c r="A52" s="241" t="s">
         <v>350</v>
       </c>
       <c r="B52" s="237"/>
@@ -20440,7 +20440,7 @@
       </c>
     </row>
     <row r="56" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A56" s="239" t="s">
+      <c r="A56" s="241" t="s">
         <v>354</v>
       </c>
       <c r="B56" s="237"/>
@@ -20560,7 +20560,7 @@
       </c>
     </row>
     <row r="60" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A60" s="239" t="s">
+      <c r="A60" s="241" t="s">
         <v>384</v>
       </c>
       <c r="B60" s="237"/>
@@ -20720,13 +20720,6 @@
   </sheetData>
   <autoFilter ref="B1:F1"/>
   <mergeCells count="17">
-    <mergeCell ref="A60:H60"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A22:H22"/>
-    <mergeCell ref="A56:H56"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A52:H52"/>
@@ -20737,6 +20730,13 @@
     <mergeCell ref="A35:H35"/>
     <mergeCell ref="A20:H20"/>
     <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A60:H60"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A56:H56"/>
   </mergeCells>
   <phoneticPr fontId="37" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
